--- a/asx_eod_output/Report_XLSX/Report_20260917.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260917.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.91</v>
+        <v>1.907</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>292575.71</v>
+        <v>292116.17</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-1531.81</v>
+        <v>-1991.35</v>
       </c>
     </row>
     <row r="5">
@@ -515,102 +515,102 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.505</v>
+        <v>2.5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>175350</v>
+        <v>175000</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>60.035</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>-0.165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>57458</v>
+        <v>8000</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>480280</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>-1320</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>60.03</v>
+        <v>0.005</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8000</v>
+        <v>44090</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>480240</v>
+        <v>220.45</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.005</v>
+        <v>153.68</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>44090</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>220.45</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
@@ -619,109 +619,109 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>CNB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>153.73</v>
+        <v>0.875</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2.19</v>
+        <v>-0.015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>8750</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CNB</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.87</v>
+        <v>177.175</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.02</v>
+        <v>2.765</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8700</v>
+        <v>708700</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-200</v>
+        <v>11060</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>E25</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>177.41</v>
+        <v>0.245</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3</v>
+        <v>-0.015</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>-5.77%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>709640</v>
+        <v>4900</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>12000</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E25</t>
+          <t>EF2</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.245</v>
+        <v>16.25</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.015</v>
+        <v>-0.25</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-5.77%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20000</v>
+        <v>3045</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4900</v>
+        <v>49481.25</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-300</v>
+        <v>-761.25</v>
       </c>
     </row>
     <row r="13">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.7</v>
+        <v>32.715</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.555</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42117.6</v>
+        <v>42136.92</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-734.16</v>
+        <v>-714.84</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1715212.96</v>
+        <v>1763053.99</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>6830.03</v>
+        <v>4428.56</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260917.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260917.xlsx
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.5</v>
+        <v>2.495</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>175000</v>
+        <v>174650</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>-350</v>
       </c>
     </row>
     <row r="6">
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>60.035</v>
+        <v>60.04</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.165</v>
+        <v>-0.16</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -556,10 +556,10 @@
         <v>8000</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>480280</v>
+        <v>480320</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1320</v>
+        <v>-1280</v>
       </c>
     </row>
     <row r="7">
@@ -596,14 +596,14 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>153.68</v>
+        <v>153.7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>177.175</v>
+        <v>177.085</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2.765</v>
+        <v>2.675</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>708700</v>
+        <v>708340</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>11060</v>
+        <v>10700</v>
       </c>
     </row>
     <row r="11">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.715</v>
+        <v>32.74</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.555</v>
+        <v>-0.53</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42136.92</v>
+        <v>42169.12</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-714.84</v>
+        <v>-682.64</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1763053.99</v>
+        <v>1762416.19</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>4428.56</v>
+        <v>3790.76</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260917.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260917.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.907</v>
+        <v>1.905</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.013</v>
+        <v>-0.015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>292116.17</v>
+        <v>291809.8</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-1991.35</v>
+        <v>-2297.71</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.495</v>
+        <v>2.5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>174650</v>
+        <v>175000</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>60.04</v>
+        <v>59.93</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.27</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>8000</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>480320</v>
+        <v>479440</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1280</v>
+        <v>-2160</v>
       </c>
     </row>
     <row r="7">
@@ -596,14 +596,14 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>153.7</v>
+        <v>154.04</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>177.085</v>
+        <v>176.95</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2.675</v>
+        <v>2.54</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>708340</v>
+        <v>707800</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10700</v>
+        <v>10160</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.245</v>
+        <v>0.25</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.015</v>
+        <v>-0.01</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-5.77%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-300</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="12">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>34.84</v>
+        <v>34.96</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.74</v>
+        <v>32.8</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-1.59%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42169.12</v>
+        <v>42246.4</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-682.64</v>
+        <v>-605.36</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1762416.19</v>
+        <v>1761217.1</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>3790.76</v>
+        <v>2591.67</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260917.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260917.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.905</v>
+        <v>1.91</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.015</v>
+        <v>-0.01</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>291809.8</v>
+        <v>292575.71</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-2297.71</v>
+        <v>-1531.81</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>175000</v>
+        <v>174300</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>-700</v>
       </c>
     </row>
     <row r="6">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>59.93</v>
+        <v>60.21</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.27</v>
+        <v>0.01</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>8000</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>479440</v>
+        <v>481680</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -596,14 +596,14 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>154.04</v>
+        <v>154.01</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -623,24 +623,24 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.875</v>
+        <v>0.86</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.015</v>
+        <v>-0.03</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>-3.37%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8750</v>
+        <v>8600</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-150</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="10">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>176.95</v>
+        <v>177.56</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>707800</v>
+        <v>710240</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10160</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="11">
@@ -785,24 +785,24 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>6000</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>34.96</v>
+        <v>34.83</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.8</v>
+        <v>32.98</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.29</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42246.4</v>
+        <v>42478.24</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-605.36</v>
+        <v>-373.52</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1761217.1</v>
+        <v>1766056.85</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>2591.67</v>
+        <v>7431.42</v>
       </c>
     </row>
   </sheetData>
